--- a/public/templates/invoice/ryoshu_advance_gyosei.xlsx
+++ b/public/templates/invoice/ryoshu_advance_gyosei.xlsx
@@ -8,10 +8,6 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="領収書（前受金）行" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <externalReferences>
-    <externalReference xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
-    <externalReference xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
-  </externalReferences>
   <definedNames>
     <definedName name="一般社団法人いきいき">抽出元!$A$3</definedName>
     <definedName name="株式会社オーシャン">抽出元!$A$4</definedName>
@@ -4363,166 +4359,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="入力元"/>
-      <sheetName val="簡易契約書 "/>
-      <sheetName val="簡易契約書 (行・司)"/>
-      <sheetName val="契約書★財産調査あり（連名）"/>
-      <sheetName val="契約書★財産調査なし（連名）"/>
-      <sheetName val="契約書★財産調査あり（行単独）"/>
-      <sheetName val="契約書(遺言など単独)★財産調査なし "/>
-      <sheetName val="委任状  (法定相続情報証明）"/>
-      <sheetName val="委任状（行・司連名）"/>
-      <sheetName val="委任状（行・司連連名）預金解約あり"/>
-      <sheetName val="委任状（行・司連名）登記のみ"/>
-      <sheetName val="委任状（行のみ）相続"/>
-      <sheetName val="委任状 (司のみ)相続登記 "/>
-      <sheetName val="委任状 (行)遺言"/>
-      <sheetName val="委任状 (行司)贈与・信託"/>
-      <sheetName val="委任状 (司)贈与・信託 "/>
-      <sheetName val="委任状 (遺言検索のみ)"/>
-      <sheetName val="原本預かり証"/>
-      <sheetName val="原本受領証"/>
-      <sheetName val="郵送書類確認票"/>
-      <sheetName val="契約書（1％）"/>
-      <sheetName val="契約書（執行）"/>
-      <sheetName val="請求書（前受金）行"/>
-      <sheetName val="請求書（前受金）司"/>
-      <sheetName val="立替実費 行 "/>
-      <sheetName val="立替実費 司"/>
-      <sheetName val="請求書 (確定)行"/>
-      <sheetName val="請求書 (確定) 司"/>
-      <sheetName val="領収書（前受金）行"/>
-      <sheetName val="領収書（前受金）司"/>
-      <sheetName val="領収書 (確定)行"/>
-      <sheetName val="領収書 (確定)司"/>
-      <sheetName val="角２封筒"/>
-      <sheetName val="長形３号（白）"/>
-      <sheetName val="長形３号 (茶)"/>
-      <sheetName val="抽出元"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
-      <sheetData sheetId="14"/>
-      <sheetData sheetId="15"/>
-      <sheetData sheetId="16"/>
-      <sheetData sheetId="17"/>
-      <sheetData sheetId="18"/>
-      <sheetData sheetId="19"/>
-      <sheetData sheetId="20"/>
-      <sheetData sheetId="21"/>
-      <sheetData sheetId="22"/>
-      <sheetData sheetId="23"/>
-      <sheetData sheetId="24"/>
-      <sheetData sheetId="25"/>
-      <sheetData sheetId="26"/>
-      <sheetData sheetId="27"/>
-      <sheetData sheetId="28"/>
-      <sheetData sheetId="29"/>
-      <sheetData sheetId="30"/>
-      <sheetData sheetId="31"/>
-      <sheetData sheetId="32"/>
-      <sheetData sheetId="33"/>
-      <sheetData sheetId="34"/>
-      <sheetData sheetId="35"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="入力元"/>
-      <sheetName val="簡易契約書 "/>
-      <sheetName val="簡易契約書 (行・司)"/>
-      <sheetName val="契約書★財産調査あり（連名）"/>
-      <sheetName val="契約書★財産調査なし（連名）"/>
-      <sheetName val="契約書★財産調査あり（行単独）"/>
-      <sheetName val="契約書(遺言など単独)★財産調査なし "/>
-      <sheetName val="委任状  (法定相続情報証明）"/>
-      <sheetName val="委任状"/>
-      <sheetName val="委任状（預金解約あり） "/>
-      <sheetName val="委任状 (登記のみ) "/>
-      <sheetName val="委任状 (遺言一般)"/>
-      <sheetName val="委任状 (贈与・信託)"/>
-      <sheetName val="委任状 (遺言検索のみ)"/>
-      <sheetName val="原本預かり証"/>
-      <sheetName val="原本受領証"/>
-      <sheetName val="郵送書類確認票"/>
-      <sheetName val="返送書類ご案内一覧 "/>
-      <sheetName val="契約書（1％）"/>
-      <sheetName val="契約書（執行）"/>
-      <sheetName val="請求書（前受金）行"/>
-      <sheetName val="請求書（前受金）司"/>
-      <sheetName val="立替実費"/>
-      <sheetName val="請求書 (確定)行"/>
-      <sheetName val="請求書 (確定) 司"/>
-      <sheetName val="領収書（前受金）行"/>
-      <sheetName val="領収書（前受金）司"/>
-      <sheetName val="領収書 (確定)行"/>
-      <sheetName val="領収書 (確定) 司"/>
-      <sheetName val="角２封筒"/>
-      <sheetName val="長形３号（白）"/>
-      <sheetName val="長形３号 (茶)"/>
-      <sheetName val="抽出元"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
-      <sheetData sheetId="6" refreshError="1"/>
-      <sheetData sheetId="7" refreshError="1"/>
-      <sheetData sheetId="8" refreshError="1"/>
-      <sheetData sheetId="9" refreshError="1"/>
-      <sheetData sheetId="10" refreshError="1"/>
-      <sheetData sheetId="11" refreshError="1"/>
-      <sheetData sheetId="12" refreshError="1"/>
-      <sheetData sheetId="13" refreshError="1"/>
-      <sheetData sheetId="14" refreshError="1"/>
-      <sheetData sheetId="15" refreshError="1"/>
-      <sheetData sheetId="16"/>
-      <sheetData sheetId="17" refreshError="1"/>
-      <sheetData sheetId="18" refreshError="1"/>
-      <sheetData sheetId="19" refreshError="1"/>
-      <sheetData sheetId="20"/>
-      <sheetData sheetId="21"/>
-      <sheetData sheetId="22" refreshError="1"/>
-      <sheetData sheetId="23"/>
-      <sheetData sheetId="24"/>
-      <sheetData sheetId="25" refreshError="1"/>
-      <sheetData sheetId="26" refreshError="1"/>
-      <sheetData sheetId="27" refreshError="1"/>
-      <sheetData sheetId="28" refreshError="1"/>
-      <sheetData sheetId="29" refreshError="1"/>
-      <sheetData sheetId="30" refreshError="1"/>
-      <sheetData sheetId="31" refreshError="1"/>
-      <sheetData sheetId="32" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>

--- a/public/templates/invoice/ryoshu_advance_gyosei.xlsx
+++ b/public/templates/invoice/ryoshu_advance_gyosei.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="10" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="10" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="領収書（前受金）行" sheetId="1" state="visible" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <definedName name="行政書士法人">抽出元!$A$1</definedName>
     <definedName name="司法書士法人">抽出元!$A$2</definedName>
     <definedName name="徽章2" localSheetId="0">INDIRECT('領収書（前受金）行'!$R$10:$V$10)</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'領収書（前受金）行'!$A$1:$Y$38</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -4560,7 +4561,7 @@
   <sheetPr>
     <tabColor rgb="FFFFC000"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AJ1000"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1" outlineLevelRow="1"/>
@@ -4753,7 +4754,7 @@
       <c r="P6" s="248" t="n"/>
       <c r="Q6" s="619" t="inlineStr">
         <is>
-          <t xml:space="preserve">　登録番号：T5-0200-0501-0814</t>
+          <t>登録番号：T5-0200-0501-0814</t>
         </is>
       </c>
       <c r="Z6" s="611" t="n"/>
@@ -5183,7 +5184,7 @@
     </row>
     <row r="17" ht="28.5" customHeight="1" s="359">
       <c r="A17" s="7" t="n"/>
-      <c r="B17" s="640" t="inlineStr">
+      <c r="B17" s="642" t="inlineStr">
         <is>
           <t>件　　　　名</t>
         </is>
@@ -42702,6 +42703,6 @@
   </dataValidations>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.7086614173228347" right="0.7086614173228347" top="0.5905511811023623" bottom="0" header="0" footer="0"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="96"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>